--- a/artfynd/A 22312-2022 artfynd.xlsx
+++ b/artfynd/A 22312-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 22312-2022 artfynd.xlsx
+++ b/artfynd/A 22312-2022 artfynd.xlsx
@@ -960,12 +960,7 @@
         <v>63225986</v>
       </c>
       <c r="B4" t="n">
-        <v>57508</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Dokumentation efterfrågas</t>
-        </is>
+        <v>56613</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,10 +1016,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593812.0102122515</v>
+        <v>593812</v>
       </c>
       <c r="R4" t="n">
-        <v>6456697.85151528</v>
+        <v>6456698</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1054,19 +1049,9 @@
           <t>2013-08-11</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2013-08-12</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">

--- a/artfynd/A 22312-2022 artfynd.xlsx
+++ b/artfynd/A 22312-2022 artfynd.xlsx
@@ -960,7 +960,7 @@
         <v>63225986</v>
       </c>
       <c r="B4" t="n">
-        <v>56613</v>
+        <v>56615</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22312-2022 artfynd.xlsx
+++ b/artfynd/A 22312-2022 artfynd.xlsx
@@ -960,7 +960,7 @@
         <v>63225986</v>
       </c>
       <c r="B4" t="n">
-        <v>56615</v>
+        <v>56617</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22312-2022 artfynd.xlsx
+++ b/artfynd/A 22312-2022 artfynd.xlsx
@@ -960,7 +960,7 @@
         <v>63225986</v>
       </c>
       <c r="B4" t="n">
-        <v>56617</v>
+        <v>56620</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
